--- a/web/public/forms/otak-sigong.xlsx
+++ b/web/public/forms/otak-sigong.xlsx
@@ -355,65 +355,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">      본 공사는 부산</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">~</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">거제간 연결 접속도로</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">가덕대교</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="굴림"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">건설공사 기간중</t>
-    </r>
+    <t xml:space="preserve">      본 공사는 해상 교량 건설공사 기간중</t>
   </si>
   <si>
     <t xml:space="preserve">준설 및 교각공사로 발생하는 오탁수 및 부유물질 확산으로 해수가 오탁</t>

--- a/web/public/forms/otak-sigong.xlsx
+++ b/web/public/forms/otak-sigong.xlsx
@@ -5267,10 +5267,10 @@
     <t xml:space="preserve">막체의 주름방지를 위한 추역활로 제품에 따라 선정</t>
   </si>
   <si>
-    <t xml:space="preserve">제  영  춘</t>
-  </si>
-  <si>
-    <t xml:space="preserve">박  영  근</t>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
   </si>
   <si>
     <t xml:space="preserve">특별인부</t>

--- a/web/public/forms/otak-sigong.xlsx
+++ b/web/public/forms/otak-sigong.xlsx
@@ -843,7 +843,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="56" t="inlineStr">
@@ -1349,7 +1349,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="56" t="inlineStr">
@@ -1724,7 +1724,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="K1" s="56" t="inlineStr">
@@ -2522,7 +2522,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="56" t="inlineStr">
@@ -2867,7 +2867,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="56" t="inlineStr">
@@ -3525,7 +3525,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="56" t="inlineStr">
@@ -3786,7 +3786,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4340,7 +4340,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6418,7 +6418,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">

--- a/web/public/forms/otak-sigong.xlsx
+++ b/web/public/forms/otak-sigong.xlsx
@@ -17,12 +17,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.투입계획" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.문제점및대책" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품질·환경·안전" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-표지" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-1.공사개요" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-2.예정공정표" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-3.조직도" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-6.투입계획" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="예시-7.문제점및대책" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'표지'!$A$1:$L$8</definedName>
@@ -35,12 +29,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="7">'6.투입계획'!$A$1:$L$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'7.문제점및대책'!$A$1:$L$10</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'품질·환경·안전'!$A$1:$L$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'예시-표지'!$A$1:$L$8</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'예시-1.공사개요'!$A$1:$L$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'예시-2.예정공정표'!$A$1:$AB$16</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="13">'예시-3.조직도'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'예시-6.투입계획'!$A$1:$L$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'예시-7.문제점및대책'!$A$1:$L$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -277,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -441,27 +429,11 @@
     </xf>
     <xf numFmtId="179" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <numFmt numFmtId="300" formatCode="#,##0&quot;m&quot;;;&quot;&quot;"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="002F5597"/>
-          <bgColor rgb="002F5597"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -901,6 +873,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="19.5" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
         <is>
@@ -1163,6 +1136,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="19.5" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
@@ -1199,2564 +1173,6 @@
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="120" customHeight="1"/>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>오 탁 방 지 막   시 공 계 획 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="80" customHeight="1"/>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>공 사 명</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>가나항 물양장 정비공사</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>제 출 일</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="8" t="n">
-        <v>46106</v>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="200" customHeight="1"/>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>예시건설(주)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="19.5" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A10:L10"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="E5:J5"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="E6:J6"/>
-    <mergeCell ref="A6:B6"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Ⅰ.  시 공 계 획</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="6" customHeight="1"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>1. 공사개요</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="16">
-        <f>"    본 공사는 "&amp;IF('예시-표지'!E5="","○○ 공사","「"&amp;'예시-표지'!E5&amp;"」")&amp;" 기간 중 준설과 기초공사로 생기는 오탁수와 부유물질이 퍼져 바다(하천)가 오탁되는 것을 막기 위하여 오탁방지막을 설치하는 공사입니다."</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" ht="6" customHeight="1"/>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>막 한 장(1 SPAN) 길이</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="17" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>앵커 간격 · 줄 수</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="18" t="n">
-        <v>10</v>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="4" customHeight="1"/>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>구  분</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>연  장</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>오탁방지막</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>닻가지형 앵커</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="20" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>1구간</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="21" t="n">
-        <v>250</v>
-      </c>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="22">
-        <f>IF(OR(N(C10)=0,N(D7)=0),"",ROUNDUP(C10/D7,0))</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="23">
-        <f>IF(OR(N(C10)=0,N(I7)=0),"",(ROUNDUP(C10/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="24" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>2구간</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="21" t="n">
-        <v>250</v>
-      </c>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="22">
-        <f>IF(OR(N(C11)=0,N(D7)=0),"",ROUNDUP(C11/D7,0))</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="23">
-        <f>IF(OR(N(C11)=0,N(I7)=0),"",(ROUNDUP(C11/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="24" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>3구간</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="21" t="n">
-        <v>1520</v>
-      </c>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="22">
-        <f>IF(OR(N(C12)=0,N(D7)=0),"",ROUNDUP(C12/D7,0))</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="23">
-        <f>IF(OR(N(C12)=0,N(I7)=0),"",(ROUNDUP(C12/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
-      <c r="I12" s="6" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="21" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="22">
-        <f>IF(OR(N(C13)=0,N(D7)=0),"",ROUNDUP(C13/D7,0))</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="23">
-        <f>IF(OR(N(C13)=0,N(I7)=0),"",(ROUNDUP(C13/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="24" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="22">
-        <f>IF(OR(N(C14)=0,N(D7)=0),"",ROUNDUP(C14/D7,0))</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="23">
-        <f>IF(OR(N(C14)=0,N(I7)=0),"",(ROUNDUP(C14/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
-      <c r="I14" s="6" t="n"/>
-      <c r="J14" s="24" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="25" t="inlineStr">
-        <is>
-          <t>합  계</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="26">
-        <f>IF(SUM(C10:C14)=0,"",SUM(C10:C14))</f>
-        <v/>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="27">
-        <f>IF(SUM(F10:F14)=0,"",SUM(F10:F14))</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="28">
-        <f>IF(SUM(H10:H14)=0,"",SUM(H10:H14))</f>
-        <v/>
-      </c>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="25" t="inlineStr"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>※ SPAN = 연장 ÷ 막 한 장 길이(올림) · 앵커 = (연장 ÷ 앵커 간격(올림) + 1) × 줄 수 — 노란 칸은 설계에 맞게 고쳐 씁니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="21.5" customHeight="1">
-      <c r="A17" s="29" t="inlineStr">
-        <is>
-          <t>※ 오랫동안 설치해 두어 오탁방지막의 평균 수명(2~3년)을 넘기면 다시 설치합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="6" customHeight="1"/>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>2. 예정공정표 (별첨)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>3. 조직도 (별첨)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="A21:L21"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J11:L11"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A17:L17"/>
-    <mergeCell ref="J12:L12"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="A19:L19"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J10:L10"/>
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="C10:E10"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C10:C15">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(C10),MOD(C10,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AB16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="2.4" customWidth="1" min="4" max="4"/>
-    <col width="2.4" customWidth="1" min="5" max="5"/>
-    <col width="2.4" customWidth="1" min="6" max="6"/>
-    <col width="2.4" customWidth="1" min="7" max="7"/>
-    <col width="2.4" customWidth="1" min="8" max="8"/>
-    <col width="2.4" customWidth="1" min="9" max="9"/>
-    <col width="2.4" customWidth="1" min="10" max="10"/>
-    <col width="2.4" customWidth="1" min="11" max="11"/>
-    <col width="2.4" customWidth="1" min="12" max="12"/>
-    <col width="2.4" customWidth="1" min="13" max="13"/>
-    <col width="2.4" customWidth="1" min="14" max="14"/>
-    <col width="2.4" customWidth="1" min="15" max="15"/>
-    <col width="2.4" customWidth="1" min="16" max="16"/>
-    <col width="2.4" customWidth="1" min="17" max="17"/>
-    <col width="2.4" customWidth="1" min="18" max="18"/>
-    <col width="2.4" customWidth="1" min="19" max="19"/>
-    <col width="2.4" customWidth="1" min="20" max="20"/>
-    <col width="2.4" customWidth="1" min="21" max="21"/>
-    <col width="2.4" customWidth="1" min="22" max="22"/>
-    <col width="2.4" customWidth="1" min="23" max="23"/>
-    <col width="2.4" customWidth="1" min="24" max="24"/>
-    <col width="2.4" customWidth="1" min="25" max="25"/>
-    <col width="2.4" customWidth="1" min="26" max="26"/>
-    <col width="2.4" customWidth="1" min="27" max="27"/>
-    <col width="9" customWidth="1" min="28" max="28"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="K1" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>2.  예 정 공 정 표</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>착 공 일</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="n">
-        <v>46113</v>
-      </c>
-      <c r="C3" s="6" t="n"/>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>※ 착공일을 적으면 달 눈금이, 공종마다 착수·완료일을 적으면 막대가 그려집니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>공    종</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>착 수</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>완 료</t>
-        </is>
-      </c>
-      <c r="D4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
-      <c r="M4" s="6" t="n"/>
-      <c r="N4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
-      <c r="O4" s="6" t="n"/>
-      <c r="P4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
-      <c r="S4" s="6" t="n"/>
-      <c r="T4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
-      <c r="U4" s="6" t="n"/>
-      <c r="V4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
-      <c r="W4" s="6" t="n"/>
-      <c r="X4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
-      <c r="Y4" s="6" t="n"/>
-      <c r="Z4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
-      <c r="AA4" s="6" t="n"/>
-      <c r="AB4" s="20" t="inlineStr">
-        <is>
-          <t>비 고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="E5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="F5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="H5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="J5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="L5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="N5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="O5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="P5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="Q5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="R5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="S5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="T5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="U5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="V5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="W5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="X5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="Y5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="Z5" s="31" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="AA5" s="31" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="AB5" s="6" t="n"/>
-    </row>
-    <row r="6" hidden="1" ht="12" customHeight="1">
-      <c r="D6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+15)</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
-      <c r="G6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+15)</f>
-        <v/>
-      </c>
-      <c r="H6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
-      <c r="I6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+15)</f>
-        <v/>
-      </c>
-      <c r="J6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
-      <c r="K6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+15)</f>
-        <v/>
-      </c>
-      <c r="L6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
-      <c r="M6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+15)</f>
-        <v/>
-      </c>
-      <c r="N6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
-      <c r="O6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+15)</f>
-        <v/>
-      </c>
-      <c r="P6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+15)</f>
-        <v/>
-      </c>
-      <c r="R6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
-      <c r="S6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+15)</f>
-        <v/>
-      </c>
-      <c r="T6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
-      <c r="U6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+15)</f>
-        <v/>
-      </c>
-      <c r="V6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
-      <c r="W6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+15)</f>
-        <v/>
-      </c>
-      <c r="X6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+15)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" hidden="1" ht="12" customHeight="1">
-      <c r="D7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+14)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)-1)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+14)</f>
-        <v/>
-      </c>
-      <c r="G7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)-1)</f>
-        <v/>
-      </c>
-      <c r="H7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+14)</f>
-        <v/>
-      </c>
-      <c r="I7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)-1)</f>
-        <v/>
-      </c>
-      <c r="J7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+14)</f>
-        <v/>
-      </c>
-      <c r="K7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)-1)</f>
-        <v/>
-      </c>
-      <c r="L7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+14)</f>
-        <v/>
-      </c>
-      <c r="M7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)-1)</f>
-        <v/>
-      </c>
-      <c r="N7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+14)</f>
-        <v/>
-      </c>
-      <c r="O7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)-1)</f>
-        <v/>
-      </c>
-      <c r="P7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+14)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)-1)</f>
-        <v/>
-      </c>
-      <c r="R7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+14)</f>
-        <v/>
-      </c>
-      <c r="S7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)-1)</f>
-        <v/>
-      </c>
-      <c r="T7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+14)</f>
-        <v/>
-      </c>
-      <c r="U7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)-1)</f>
-        <v/>
-      </c>
-      <c r="V7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+14)</f>
-        <v/>
-      </c>
-      <c r="W7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)-1)</f>
-        <v/>
-      </c>
-      <c r="X7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+14)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)-1)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+14)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),12)-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="33" t="inlineStr">
-        <is>
-          <t>오탁방지막 제작</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="n">
-        <v>46113</v>
-      </c>
-      <c r="C8" s="34" t="n">
-        <v>46132</v>
-      </c>
-      <c r="D8" s="35" t="inlineStr"/>
-      <c r="E8" s="35" t="inlineStr"/>
-      <c r="F8" s="35" t="inlineStr"/>
-      <c r="G8" s="35" t="inlineStr"/>
-      <c r="H8" s="35" t="inlineStr"/>
-      <c r="I8" s="35" t="inlineStr"/>
-      <c r="J8" s="35" t="inlineStr"/>
-      <c r="K8" s="35" t="inlineStr"/>
-      <c r="L8" s="35" t="inlineStr"/>
-      <c r="M8" s="35" t="inlineStr"/>
-      <c r="N8" s="35" t="inlineStr"/>
-      <c r="O8" s="35" t="inlineStr"/>
-      <c r="P8" s="35" t="inlineStr"/>
-      <c r="Q8" s="35" t="inlineStr"/>
-      <c r="R8" s="35" t="inlineStr"/>
-      <c r="S8" s="35" t="inlineStr"/>
-      <c r="T8" s="35" t="inlineStr"/>
-      <c r="U8" s="35" t="inlineStr"/>
-      <c r="V8" s="35" t="inlineStr"/>
-      <c r="W8" s="35" t="inlineStr"/>
-      <c r="X8" s="35" t="inlineStr"/>
-      <c r="Y8" s="35" t="inlineStr"/>
-      <c r="Z8" s="35" t="inlineStr"/>
-      <c r="AA8" s="35" t="inlineStr"/>
-      <c r="AB8" s="36" t="n"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>닻(앵커) 제작</t>
-        </is>
-      </c>
-      <c r="B9" s="34" t="n">
-        <v>46113</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <v>46132</v>
-      </c>
-      <c r="D9" s="35" t="inlineStr"/>
-      <c r="E9" s="35" t="inlineStr"/>
-      <c r="F9" s="35" t="inlineStr"/>
-      <c r="G9" s="35" t="inlineStr"/>
-      <c r="H9" s="35" t="inlineStr"/>
-      <c r="I9" s="35" t="inlineStr"/>
-      <c r="J9" s="35" t="inlineStr"/>
-      <c r="K9" s="35" t="inlineStr"/>
-      <c r="L9" s="35" t="inlineStr"/>
-      <c r="M9" s="35" t="inlineStr"/>
-      <c r="N9" s="35" t="inlineStr"/>
-      <c r="O9" s="35" t="inlineStr"/>
-      <c r="P9" s="35" t="inlineStr"/>
-      <c r="Q9" s="35" t="inlineStr"/>
-      <c r="R9" s="35" t="inlineStr"/>
-      <c r="S9" s="35" t="inlineStr"/>
-      <c r="T9" s="35" t="inlineStr"/>
-      <c r="U9" s="35" t="inlineStr"/>
-      <c r="V9" s="35" t="inlineStr"/>
-      <c r="W9" s="35" t="inlineStr"/>
-      <c r="X9" s="35" t="inlineStr"/>
-      <c r="Y9" s="35" t="inlineStr"/>
-      <c r="Z9" s="35" t="inlineStr"/>
-      <c r="AA9" s="35" t="inlineStr"/>
-      <c r="AB9" s="36" t="n"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="33" t="inlineStr">
-        <is>
-          <t>오탁방지막 설치</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="n">
-        <v>46133</v>
-      </c>
-      <c r="C10" s="34" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D10" s="35" t="inlineStr"/>
-      <c r="E10" s="35" t="inlineStr"/>
-      <c r="F10" s="35" t="inlineStr"/>
-      <c r="G10" s="35" t="inlineStr"/>
-      <c r="H10" s="35" t="inlineStr"/>
-      <c r="I10" s="35" t="inlineStr"/>
-      <c r="J10" s="35" t="inlineStr"/>
-      <c r="K10" s="35" t="inlineStr"/>
-      <c r="L10" s="35" t="inlineStr"/>
-      <c r="M10" s="35" t="inlineStr"/>
-      <c r="N10" s="35" t="inlineStr"/>
-      <c r="O10" s="35" t="inlineStr"/>
-      <c r="P10" s="35" t="inlineStr"/>
-      <c r="Q10" s="35" t="inlineStr"/>
-      <c r="R10" s="35" t="inlineStr"/>
-      <c r="S10" s="35" t="inlineStr"/>
-      <c r="T10" s="35" t="inlineStr"/>
-      <c r="U10" s="35" t="inlineStr"/>
-      <c r="V10" s="35" t="inlineStr"/>
-      <c r="W10" s="35" t="inlineStr"/>
-      <c r="X10" s="35" t="inlineStr"/>
-      <c r="Y10" s="35" t="inlineStr"/>
-      <c r="Z10" s="35" t="inlineStr"/>
-      <c r="AA10" s="35" t="inlineStr"/>
-      <c r="AB10" s="36" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>닻(앵커) 설치</t>
-        </is>
-      </c>
-      <c r="B11" s="34" t="n">
-        <v>46133</v>
-      </c>
-      <c r="C11" s="34" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D11" s="35" t="inlineStr"/>
-      <c r="E11" s="35" t="inlineStr"/>
-      <c r="F11" s="35" t="inlineStr"/>
-      <c r="G11" s="35" t="inlineStr"/>
-      <c r="H11" s="35" t="inlineStr"/>
-      <c r="I11" s="35" t="inlineStr"/>
-      <c r="J11" s="35" t="inlineStr"/>
-      <c r="K11" s="35" t="inlineStr"/>
-      <c r="L11" s="35" t="inlineStr"/>
-      <c r="M11" s="35" t="inlineStr"/>
-      <c r="N11" s="35" t="inlineStr"/>
-      <c r="O11" s="35" t="inlineStr"/>
-      <c r="P11" s="35" t="inlineStr"/>
-      <c r="Q11" s="35" t="inlineStr"/>
-      <c r="R11" s="35" t="inlineStr"/>
-      <c r="S11" s="35" t="inlineStr"/>
-      <c r="T11" s="35" t="inlineStr"/>
-      <c r="U11" s="35" t="inlineStr"/>
-      <c r="V11" s="35" t="inlineStr"/>
-      <c r="W11" s="35" t="inlineStr"/>
-      <c r="X11" s="35" t="inlineStr"/>
-      <c r="Y11" s="35" t="inlineStr"/>
-      <c r="Z11" s="35" t="inlineStr"/>
-      <c r="AA11" s="35" t="inlineStr"/>
-      <c r="AB11" s="36" t="n"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="33" t="inlineStr">
-        <is>
-          <t>유지보수(월 1회 점검)</t>
-        </is>
-      </c>
-      <c r="B12" s="34" t="n">
-        <v>46158</v>
-      </c>
-      <c r="C12" s="34" t="n">
-        <v>46446</v>
-      </c>
-      <c r="D12" s="35" t="inlineStr"/>
-      <c r="E12" s="35" t="inlineStr"/>
-      <c r="F12" s="35" t="inlineStr"/>
-      <c r="G12" s="35" t="inlineStr"/>
-      <c r="H12" s="35" t="inlineStr"/>
-      <c r="I12" s="35" t="inlineStr"/>
-      <c r="J12" s="35" t="inlineStr"/>
-      <c r="K12" s="35" t="inlineStr"/>
-      <c r="L12" s="35" t="inlineStr"/>
-      <c r="M12" s="35" t="inlineStr"/>
-      <c r="N12" s="35" t="inlineStr"/>
-      <c r="O12" s="35" t="inlineStr"/>
-      <c r="P12" s="35" t="inlineStr"/>
-      <c r="Q12" s="35" t="inlineStr"/>
-      <c r="R12" s="35" t="inlineStr"/>
-      <c r="S12" s="35" t="inlineStr"/>
-      <c r="T12" s="35" t="inlineStr"/>
-      <c r="U12" s="35" t="inlineStr"/>
-      <c r="V12" s="35" t="inlineStr"/>
-      <c r="W12" s="35" t="inlineStr"/>
-      <c r="X12" s="35" t="inlineStr"/>
-      <c r="Y12" s="35" t="inlineStr"/>
-      <c r="Z12" s="35" t="inlineStr"/>
-      <c r="AA12" s="35" t="inlineStr"/>
-      <c r="AB12" s="36" t="inlineStr">
-        <is>
-          <t>월 1회</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
-        <is>
-          <t>오탁방지막 철수</t>
-        </is>
-      </c>
-      <c r="B13" s="34" t="n">
-        <v>46447</v>
-      </c>
-      <c r="C13" s="34" t="n">
-        <v>46461</v>
-      </c>
-      <c r="D13" s="35" t="inlineStr"/>
-      <c r="E13" s="35" t="inlineStr"/>
-      <c r="F13" s="35" t="inlineStr"/>
-      <c r="G13" s="35" t="inlineStr"/>
-      <c r="H13" s="35" t="inlineStr"/>
-      <c r="I13" s="35" t="inlineStr"/>
-      <c r="J13" s="35" t="inlineStr"/>
-      <c r="K13" s="35" t="inlineStr"/>
-      <c r="L13" s="35" t="inlineStr"/>
-      <c r="M13" s="35" t="inlineStr"/>
-      <c r="N13" s="35" t="inlineStr"/>
-      <c r="O13" s="35" t="inlineStr"/>
-      <c r="P13" s="35" t="inlineStr"/>
-      <c r="Q13" s="35" t="inlineStr"/>
-      <c r="R13" s="35" t="inlineStr"/>
-      <c r="S13" s="35" t="inlineStr"/>
-      <c r="T13" s="35" t="inlineStr"/>
-      <c r="U13" s="35" t="inlineStr"/>
-      <c r="V13" s="35" t="inlineStr"/>
-      <c r="W13" s="35" t="inlineStr"/>
-      <c r="X13" s="35" t="inlineStr"/>
-      <c r="Y13" s="35" t="inlineStr"/>
-      <c r="Z13" s="35" t="inlineStr"/>
-      <c r="AA13" s="35" t="inlineStr"/>
-      <c r="AB13" s="36" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="33" t="n"/>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="35" t="inlineStr"/>
-      <c r="E14" s="35" t="inlineStr"/>
-      <c r="F14" s="35" t="inlineStr"/>
-      <c r="G14" s="35" t="inlineStr"/>
-      <c r="H14" s="35" t="inlineStr"/>
-      <c r="I14" s="35" t="inlineStr"/>
-      <c r="J14" s="35" t="inlineStr"/>
-      <c r="K14" s="35" t="inlineStr"/>
-      <c r="L14" s="35" t="inlineStr"/>
-      <c r="M14" s="35" t="inlineStr"/>
-      <c r="N14" s="35" t="inlineStr"/>
-      <c r="O14" s="35" t="inlineStr"/>
-      <c r="P14" s="35" t="inlineStr"/>
-      <c r="Q14" s="35" t="inlineStr"/>
-      <c r="R14" s="35" t="inlineStr"/>
-      <c r="S14" s="35" t="inlineStr"/>
-      <c r="T14" s="35" t="inlineStr"/>
-      <c r="U14" s="35" t="inlineStr"/>
-      <c r="V14" s="35" t="inlineStr"/>
-      <c r="W14" s="35" t="inlineStr"/>
-      <c r="X14" s="35" t="inlineStr"/>
-      <c r="Y14" s="35" t="inlineStr"/>
-      <c r="Z14" s="35" t="inlineStr"/>
-      <c r="AA14" s="35" t="inlineStr"/>
-      <c r="AB14" s="36" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="33" t="n"/>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="35" t="inlineStr"/>
-      <c r="E15" s="35" t="inlineStr"/>
-      <c r="F15" s="35" t="inlineStr"/>
-      <c r="G15" s="35" t="inlineStr"/>
-      <c r="H15" s="35" t="inlineStr"/>
-      <c r="I15" s="35" t="inlineStr"/>
-      <c r="J15" s="35" t="inlineStr"/>
-      <c r="K15" s="35" t="inlineStr"/>
-      <c r="L15" s="35" t="inlineStr"/>
-      <c r="M15" s="35" t="inlineStr"/>
-      <c r="N15" s="35" t="inlineStr"/>
-      <c r="O15" s="35" t="inlineStr"/>
-      <c r="P15" s="35" t="inlineStr"/>
-      <c r="Q15" s="35" t="inlineStr"/>
-      <c r="R15" s="35" t="inlineStr"/>
-      <c r="S15" s="35" t="inlineStr"/>
-      <c r="T15" s="35" t="inlineStr"/>
-      <c r="U15" s="35" t="inlineStr"/>
-      <c r="V15" s="35" t="inlineStr"/>
-      <c r="W15" s="35" t="inlineStr"/>
-      <c r="X15" s="35" t="inlineStr"/>
-      <c r="Y15" s="35" t="inlineStr"/>
-      <c r="Z15" s="35" t="inlineStr"/>
-      <c r="AA15" s="35" t="inlineStr"/>
-      <c r="AB15" s="36" t="n"/>
-    </row>
-    <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>※ 오랫동안 설치해 두어 오탁방지막의 평균 수명(2~3년)을 넘기면 다시 설치합니다.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A2:AB2"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="K1:AB1"/>
-    <mergeCell ref="AB4:AB5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="D3:AB3"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="A16:AB16"/>
-    <mergeCell ref="Z4:AA4"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="N4:O4"/>
-  </mergeCells>
-  <conditionalFormatting sqref="D8:AA15">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND(N($B8)&gt;0,N($C8)&gt;=N($B8),$B8&lt;=D$7,$C8&gt;=D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>3.  조 직 도</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr"/>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>직  책</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="20" t="inlineStr">
-        <is>
-          <t>성  명</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="20" t="inlineStr">
-        <is>
-          <t>맡은 일</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="4" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>공사 과장</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="37" t="inlineStr">
-        <is>
-          <t>공사 총괄 · 감독(감리) 협의</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="4" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>작업반 소장</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>이반장</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="37" t="inlineStr">
-        <is>
-          <t>작업 지휘 · 안전</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="4" t="inlineStr"/>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>작업반장</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>박반장</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="37" t="inlineStr">
-        <is>
-          <t>작업 배치 · 자재</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="4" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>잠수사</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>최잠수</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="37" t="inlineStr">
-        <is>
-          <t>수중 설치 · 점검</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>잠수사</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>정잠수</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="37" t="inlineStr">
-        <is>
-          <t>수중 설치 · 점검</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>특별인부</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>6명</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="37" t="inlineStr">
-        <is>
-          <t>육상 조립 · 운반 보조</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="14" customHeight="1"/>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="4" t="inlineStr"/>
-      <c r="E13" s="38" t="inlineStr">
-        <is>
-          <t>공사 과장</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="39" t="inlineStr"/>
-    </row>
-    <row r="14" ht="12" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="E15" s="38" t="inlineStr">
-        <is>
-          <t>작업반 소장</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="39" t="inlineStr"/>
-    </row>
-    <row r="16" ht="12" customHeight="1">
-      <c r="A16" s="40" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="E17" s="38" t="inlineStr">
-        <is>
-          <t>작업반장</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="39" t="inlineStr"/>
-    </row>
-    <row r="18" ht="12" customHeight="1">
-      <c r="A18" s="40" t="inlineStr">
-        <is>
-          <t>▼</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="E19" s="38" t="inlineStr">
-        <is>
-          <t>잠수사 · 특별인부</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="39" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="39">
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="I17:L17"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="E6:G6"/>
-    <mergeCell ref="H5:K5"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="E11:G11"/>
-    <mergeCell ref="H8:K8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A14:L14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="E13:H13"/>
-    <mergeCell ref="E5:G5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="H7:K7"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>6.  인원 · 장비 · 자재 투입계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="3" customHeight="1"/>
-    <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>6.1 작업인원 투입계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>직  종</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>일투입</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>투입일수</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>누  계</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="20" t="inlineStr">
-        <is>
-          <t>작 업 내 용</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>관리</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>인</t>
-        </is>
-      </c>
-      <c r="D7" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="49" t="n">
-        <v>40</v>
-      </c>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="50">
-        <f>IF(OR(N(D7)=0,N(E7)=0),"",D7*E7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>현장 기술지도 및 안전관리</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>반장</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>인</t>
-        </is>
-      </c>
-      <c r="D8" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="49" t="n">
-        <v>40</v>
-      </c>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="50">
-        <f>IF(OR(N(D8)=0,N(E8)=0),"",D8*E8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>현장관리 및 작업관리</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>잠수사</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>인</t>
-        </is>
-      </c>
-      <c r="D9" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="49" t="n">
-        <v>30</v>
-      </c>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="50">
-        <f>IF(OR(N(D9)=0,N(E9)=0),"",D9*E9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>오탁방지막 설치 및 닻 설치</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>특별인부</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>인</t>
-        </is>
-      </c>
-      <c r="D10" s="48" t="n">
-        <v>6</v>
-      </c>
-      <c r="E10" s="49" t="n">
-        <v>40</v>
-      </c>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="50">
-        <f>IF(OR(N(D10)=0,N(E10)=0),"",D10*E10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>오탁방지막 설치 및 닻 설치</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>인</t>
-        </is>
-      </c>
-      <c r="D11" s="48" t="n"/>
-      <c r="E11" s="49" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="50">
-        <f>IF(OR(N(D11)=0,N(E11)=0),"",D11*E11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>인</t>
-        </is>
-      </c>
-      <c r="D12" s="48" t="n"/>
-      <c r="E12" s="49" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="50">
-        <f>IF(OR(N(D12)=0,N(E12)=0),"",D12*E12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="51">
-        <f>IF(SUM(G7:G12)=0,"",SUM(G7:G12))</f>
-        <v/>
-      </c>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="25" t="inlineStr"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="3" customHeight="1"/>
-    <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="41" t="inlineStr">
-        <is>
-          <t>6.2 장비 투입계획</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>장 비 명</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>규  격</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>단위</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>일투입</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>투입일수</t>
-        </is>
-      </c>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>누  계</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="n"/>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>바지(PONTOON)</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>5m×5m</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="F17" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="49" t="n">
-        <v>25</v>
-      </c>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="52">
-        <f>IF(OR(N(F17)=0,N(G17)=0),"",F17*G17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="6" t="n"/>
-      <c r="K17" s="24" t="n"/>
-      <c r="L17" s="6" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>예선</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>150HP</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="F18" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="49" t="n">
-        <v>25</v>
-      </c>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="52">
-        <f>IF(OR(N(F18)=0,N(G18)=0),"",F18*G18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="24" t="n"/>
-      <c r="L18" s="6" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>작업선</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>모터보트</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="F19" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="49" t="n">
-        <v>40</v>
-      </c>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="52">
-        <f>IF(OR(N(F19)=0,N(G19)=0),"",F19*G19)</f>
-        <v/>
-      </c>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="24" t="n"/>
-      <c r="L19" s="6" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>크레인</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>25톤</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="F20" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" s="49" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="52">
-        <f>IF(OR(N(F20)=0,N(G20)=0),"",F20*G20)</f>
-        <v/>
-      </c>
-      <c r="J20" s="6" t="n"/>
-      <c r="K20" s="24" t="inlineStr">
-        <is>
-          <t>닻 상차</t>
-        </is>
-      </c>
-      <c r="L20" s="6" t="n"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>카고트럭</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>11톤</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="F21" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="52">
-        <f>IF(OR(N(F21)=0,N(G21)=0),"",F21*G21)</f>
-        <v/>
-      </c>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="24" t="inlineStr">
-        <is>
-          <t>자재 운반</t>
-        </is>
-      </c>
-      <c r="L21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>대</t>
-        </is>
-      </c>
-      <c r="F22" s="48" t="n"/>
-      <c r="G22" s="49" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="52">
-        <f>IF(OR(N(F22)=0,N(G22)=0),"",F22*G22)</f>
-        <v/>
-      </c>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="24" t="n"/>
-      <c r="L22" s="6" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="25" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="53">
-        <f>IF(SUM(I17:I22)=0,"",SUM(I17:I22))</f>
-        <v/>
-      </c>
-      <c r="J23" s="6" t="n"/>
-      <c r="K23" s="25" t="inlineStr"/>
-      <c r="L23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="3" customHeight="1"/>
-    <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="41" t="inlineStr">
-        <is>
-          <t>6.3 자재</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="37" customHeight="1">
-      <c r="A26" s="42" t="inlineStr">
-        <is>
-          <t>오탁방지막(막체) · 부체 · 체인 · 샤클 · 앵커(닻) · 와이어로프 — 수량은 1. 공사개요의 SPAN 수와 앵커 수를 따릅니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t>※ 작업 인원과 장비 투입은 현장 여건과 투입 날짜에 따라 바뀔 수 있습니다. 누계 = 일투입 × 투입일수.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A26:L26"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A25:L25"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="I11:L11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="I12:L12"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="7.6" customWidth="1" min="1" max="1"/>
-    <col width="7.6" customWidth="1" min="2" max="2"/>
-    <col width="7.6" customWidth="1" min="3" max="3"/>
-    <col width="7.6" customWidth="1" min="4" max="4"/>
-    <col width="7.6" customWidth="1" min="5" max="5"/>
-    <col width="7.6" customWidth="1" min="6" max="6"/>
-    <col width="7.6" customWidth="1" min="7" max="7"/>
-    <col width="7.6" customWidth="1" min="8" max="8"/>
-    <col width="7.6" customWidth="1" min="9" max="9"/>
-    <col width="7.6" customWidth="1" min="10" max="10"/>
-    <col width="7.6" customWidth="1" min="11" max="11"/>
-    <col width="7.6" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>7.  오탁방지막 설치 문제점 및 대책 검토안</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>구  분</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>문 제 점</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>대 책 검 토 안</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
-      <c r="J4" s="6" t="n"/>
-      <c r="K4" s="20" t="inlineStr">
-        <is>
-          <t>비  고</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="50" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>해상 가시설 설치</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t>가시설(가이드 프레임) 항타 때 작업 바지선의 앵커와 오탁방지막 앵커가 겹치고, 앵커 줄이 길어짐 · 자재를 나를 해상장비 항로가 없음</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-      <c r="G5" s="24" t="inlineStr">
-        <is>
-          <t>① 오탁방지막 설치 위치를 현장 여건에 맞게 다시 잡음 ② 공정이 바뀌면 준설 면적이 늘어나는지 검토 ③ 해상장비 항로·수심 확인</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-      <c r="J5" s="6" t="n"/>
-      <c r="K5" s="36" t="inlineStr">
-        <is>
-          <t>여건이 바뀌면 설치 위치·수심을 다시 검토해 계획서를 고침</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="50" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>현장타설 말뚝 · 기초</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="24" t="inlineStr">
-        <is>
-          <t>가시설 위로 대형 크레인·천공장비를 올리고 작업 바지(SEP)를 고정할 때 앵커 줄이 길어짐 · 콘크리트 타설 장비(펌프카·레미콘 운반 바지)의 항로</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="6" t="n"/>
-      <c r="G6" s="24" t="inlineStr">
-        <is>
-          <t>① 자재 운반·해상장비 항로를 검토해 수심 항로 확보 ② 설치 위치 재조정 ③ 해체·이동 때도 같은 방법</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-      <c r="J6" s="6" t="n"/>
-      <c r="K6" s="36" t="inlineStr">
-        <is>
-          <t>여건이 바뀌면 설치 위치·수심을 다시 검토해 계획서를 고침</t>
-        </is>
-      </c>
-      <c r="L6" s="6" t="n"/>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>굴착 · 가시설 보강</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>굴착과 함께 버팀보를 설치하는 동안 굴착 토사를 나를 해상장비 항로가 없음</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>① 토사 운반 항로 확보 ② 설치 위치 재조정 ③ 준설 면적 증가 검토</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="36" t="inlineStr">
-        <is>
-          <t>여건이 바뀌면 설치 위치·수심을 다시 검토해 계획서를 고침</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="n"/>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>교각 · 상부공(강교 거치)</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="24" t="inlineStr">
-        <is>
-          <t>대형 부재를 운반 바지에서 인양해 거치할 때 윈치·와이어로 바지를 앞뒤로 움직이므로 앵커 줄이 더 길어짐</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="24" t="inlineStr">
-        <is>
-          <t>① 거치 순서에 맞춰 오탁방지막을 옮겨 달거나 여닫는 구간을 둠 ② 항로·수심 확인 ③ 설치 위치 재조정</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="36" t="inlineStr">
-        <is>
-          <t>여건이 바뀌면 설치 위치·수심을 다시 검토해 계획서를 고침</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="n"/>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-      <c r="J9" s="6" t="n"/>
-      <c r="K9" s="36" t="n"/>
-      <c r="L9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-      <c r="J10" s="6" t="n"/>
-      <c r="K10" s="36" t="n"/>
-      <c r="L10" s="6" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="G5:J5"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4009,10 +1425,7 @@
       </c>
     </row>
     <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="16">
-        <f>"    본 공사는 "&amp;IF('표지'!E5="","○○ 공사","「"&amp;'표지'!E5&amp;"」")&amp;" 기간 중 준설과 기초공사로 생기는 오탁수와 부유물질이 퍼져 바다(하천)가 오탁되는 것을 막기 위하여 오탁방지막을 설치하는 공사입니다."</f>
-        <v/>
-      </c>
+      <c r="A5" s="16" t="n"/>
     </row>
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="24" customHeight="1">
@@ -4084,15 +1497,9 @@
       <c r="C10" s="21" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="22">
-        <f>IF(OR(N(C10)=0,N(D7)=0),"",ROUNDUP(C10/D7,0))</f>
-        <v/>
-      </c>
+      <c r="F10" s="22" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="23">
-        <f>IF(OR(N(C10)=0,N(I7)=0),"",(ROUNDUP(C10/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
+      <c r="H10" s="23" t="n"/>
       <c r="I10" s="6" t="n"/>
       <c r="J10" s="24" t="n"/>
       <c r="K10" s="6" t="n"/>
@@ -4104,15 +1511,9 @@
       <c r="C11" s="21" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="22">
-        <f>IF(OR(N(C11)=0,N(D7)=0),"",ROUNDUP(C11/D7,0))</f>
-        <v/>
-      </c>
+      <c r="F11" s="22" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="23">
-        <f>IF(OR(N(C11)=0,N(I7)=0),"",(ROUNDUP(C11/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
+      <c r="H11" s="23" t="n"/>
       <c r="I11" s="6" t="n"/>
       <c r="J11" s="24" t="n"/>
       <c r="K11" s="6" t="n"/>
@@ -4124,15 +1525,9 @@
       <c r="C12" s="21" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="22">
-        <f>IF(OR(N(C12)=0,N(D7)=0),"",ROUNDUP(C12/D7,0))</f>
-        <v/>
-      </c>
+      <c r="F12" s="22" t="n"/>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="23">
-        <f>IF(OR(N(C12)=0,N(I7)=0),"",(ROUNDUP(C12/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
+      <c r="H12" s="23" t="n"/>
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="24" t="n"/>
       <c r="K12" s="6" t="n"/>
@@ -4144,15 +1539,9 @@
       <c r="C13" s="21" t="n"/>
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
-      <c r="F13" s="22">
-        <f>IF(OR(N(C13)=0,N(D7)=0),"",ROUNDUP(C13/D7,0))</f>
-        <v/>
-      </c>
+      <c r="F13" s="22" t="n"/>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="23">
-        <f>IF(OR(N(C13)=0,N(I7)=0),"",(ROUNDUP(C13/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
+      <c r="H13" s="23" t="n"/>
       <c r="I13" s="6" t="n"/>
       <c r="J13" s="24" t="n"/>
       <c r="K13" s="6" t="n"/>
@@ -4164,15 +1553,9 @@
       <c r="C14" s="21" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="22">
-        <f>IF(OR(N(C14)=0,N(D7)=0),"",ROUNDUP(C14/D7,0))</f>
-        <v/>
-      </c>
+      <c r="F14" s="22" t="n"/>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="23">
-        <f>IF(OR(N(C14)=0,N(I7)=0),"",(ROUNDUP(C14/I7,0)+1)*N(K7))</f>
-        <v/>
-      </c>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="24" t="n"/>
       <c r="K14" s="6" t="n"/>
@@ -4185,21 +1568,12 @@
         </is>
       </c>
       <c r="B15" s="6" t="n"/>
-      <c r="C15" s="26">
-        <f>IF(SUM(C10:C14)=0,"",SUM(C10:C14))</f>
-        <v/>
-      </c>
+      <c r="C15" s="26" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="6" t="n"/>
-      <c r="F15" s="27">
-        <f>IF(SUM(F10:F14)=0,"",SUM(F10:F14))</f>
-        <v/>
-      </c>
+      <c r="F15" s="27" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="28">
-        <f>IF(SUM(H10:H14)=0,"",SUM(H10:H14))</f>
-        <v/>
-      </c>
+      <c r="H15" s="28" t="n"/>
       <c r="I15" s="6" t="n"/>
       <c r="J15" s="25" t="inlineStr"/>
       <c r="K15" s="6" t="n"/>
@@ -4287,11 +1661,6 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="C10:E10"/>
   </mergeCells>
-  <conditionalFormatting sqref="C10:C15">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND(ISNUMBER(C10),MOD(C10,1)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.45" right="0.45" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4386,65 +1755,29 @@
           <t>완 료</t>
         </is>
       </c>
-      <c r="D4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
+      <c r="D4" s="30" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
+      <c r="F4" s="30" t="n"/>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
+      <c r="H4" s="30" t="n"/>
       <c r="I4" s="6" t="n"/>
-      <c r="J4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
+      <c r="J4" s="30" t="n"/>
       <c r="K4" s="6" t="n"/>
-      <c r="L4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
+      <c r="L4" s="30" t="n"/>
       <c r="M4" s="6" t="n"/>
-      <c r="N4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
+      <c r="N4" s="30" t="n"/>
       <c r="O4" s="6" t="n"/>
-      <c r="P4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
+      <c r="P4" s="30" t="n"/>
       <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
+      <c r="R4" s="30" t="n"/>
       <c r="S4" s="6" t="n"/>
-      <c r="T4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
+      <c r="T4" s="30" t="n"/>
       <c r="U4" s="6" t="n"/>
-      <c r="V4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
+      <c r="V4" s="30" t="n"/>
       <c r="W4" s="6" t="n"/>
-      <c r="X4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
+      <c r="X4" s="30" t="n"/>
       <c r="Y4" s="6" t="n"/>
-      <c r="Z4" s="30">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
+      <c r="Z4" s="30" t="n"/>
       <c r="AA4" s="6" t="n"/>
       <c r="AB4" s="20" t="inlineStr">
         <is>
@@ -4579,200 +1912,56 @@
       <c r="AB5" s="6" t="n"/>
     </row>
     <row r="6" hidden="1" ht="12" customHeight="1">
-      <c r="D6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0))</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+15)</f>
-        <v/>
-      </c>
-      <c r="F6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1))</f>
-        <v/>
-      </c>
-      <c r="G6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+15)</f>
-        <v/>
-      </c>
-      <c r="H6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2))</f>
-        <v/>
-      </c>
-      <c r="I6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+15)</f>
-        <v/>
-      </c>
-      <c r="J6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3))</f>
-        <v/>
-      </c>
-      <c r="K6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+15)</f>
-        <v/>
-      </c>
-      <c r="L6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4))</f>
-        <v/>
-      </c>
-      <c r="M6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+15)</f>
-        <v/>
-      </c>
-      <c r="N6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5))</f>
-        <v/>
-      </c>
-      <c r="O6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+15)</f>
-        <v/>
-      </c>
-      <c r="P6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6))</f>
-        <v/>
-      </c>
-      <c r="Q6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+15)</f>
-        <v/>
-      </c>
-      <c r="R6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7))</f>
-        <v/>
-      </c>
-      <c r="S6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+15)</f>
-        <v/>
-      </c>
-      <c r="T6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8))</f>
-        <v/>
-      </c>
-      <c r="U6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+15)</f>
-        <v/>
-      </c>
-      <c r="V6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9))</f>
-        <v/>
-      </c>
-      <c r="W6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+15)</f>
-        <v/>
-      </c>
-      <c r="X6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10))</f>
-        <v/>
-      </c>
-      <c r="Y6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+15)</f>
-        <v/>
-      </c>
-      <c r="Z6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11))</f>
-        <v/>
-      </c>
-      <c r="AA6" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+15)</f>
-        <v/>
-      </c>
+      <c r="D6" s="32" t="n"/>
+      <c r="E6" s="32" t="n"/>
+      <c r="F6" s="32" t="n"/>
+      <c r="G6" s="32" t="n"/>
+      <c r="H6" s="32" t="n"/>
+      <c r="I6" s="32" t="n"/>
+      <c r="J6" s="32" t="n"/>
+      <c r="K6" s="32" t="n"/>
+      <c r="L6" s="32" t="n"/>
+      <c r="M6" s="32" t="n"/>
+      <c r="N6" s="32" t="n"/>
+      <c r="O6" s="32" t="n"/>
+      <c r="P6" s="32" t="n"/>
+      <c r="Q6" s="32" t="n"/>
+      <c r="R6" s="32" t="n"/>
+      <c r="S6" s="32" t="n"/>
+      <c r="T6" s="32" t="n"/>
+      <c r="U6" s="32" t="n"/>
+      <c r="V6" s="32" t="n"/>
+      <c r="W6" s="32" t="n"/>
+      <c r="X6" s="32" t="n"/>
+      <c r="Y6" s="32" t="n"/>
+      <c r="Z6" s="32" t="n"/>
+      <c r="AA6" s="32" t="n"/>
     </row>
     <row r="7" hidden="1" ht="12" customHeight="1">
-      <c r="D7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),0)+14)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)-1)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),1)+14)</f>
-        <v/>
-      </c>
-      <c r="G7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)-1)</f>
-        <v/>
-      </c>
-      <c r="H7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),2)+14)</f>
-        <v/>
-      </c>
-      <c r="I7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)-1)</f>
-        <v/>
-      </c>
-      <c r="J7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),3)+14)</f>
-        <v/>
-      </c>
-      <c r="K7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)-1)</f>
-        <v/>
-      </c>
-      <c r="L7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),4)+14)</f>
-        <v/>
-      </c>
-      <c r="M7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)-1)</f>
-        <v/>
-      </c>
-      <c r="N7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),5)+14)</f>
-        <v/>
-      </c>
-      <c r="O7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)-1)</f>
-        <v/>
-      </c>
-      <c r="P7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),6)+14)</f>
-        <v/>
-      </c>
-      <c r="Q7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)-1)</f>
-        <v/>
-      </c>
-      <c r="R7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),7)+14)</f>
-        <v/>
-      </c>
-      <c r="S7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)-1)</f>
-        <v/>
-      </c>
-      <c r="T7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),8)+14)</f>
-        <v/>
-      </c>
-      <c r="U7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)-1)</f>
-        <v/>
-      </c>
-      <c r="V7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),9)+14)</f>
-        <v/>
-      </c>
-      <c r="W7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)-1)</f>
-        <v/>
-      </c>
-      <c r="X7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),10)+14)</f>
-        <v/>
-      </c>
-      <c r="Y7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)-1)</f>
-        <v/>
-      </c>
-      <c r="Z7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),11)+14)</f>
-        <v/>
-      </c>
-      <c r="AA7" s="32">
-        <f>IF(N(B3)=0,"",EDATE(DATE(YEAR(B3),MONTH(B3),1),12)-1)</f>
-        <v/>
-      </c>
+      <c r="D7" s="32" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="32" t="n"/>
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="32" t="n"/>
+      <c r="J7" s="32" t="n"/>
+      <c r="K7" s="32" t="n"/>
+      <c r="L7" s="32" t="n"/>
+      <c r="M7" s="32" t="n"/>
+      <c r="N7" s="32" t="n"/>
+      <c r="O7" s="32" t="n"/>
+      <c r="P7" s="32" t="n"/>
+      <c r="Q7" s="32" t="n"/>
+      <c r="R7" s="32" t="n"/>
+      <c r="S7" s="32" t="n"/>
+      <c r="T7" s="32" t="n"/>
+      <c r="U7" s="32" t="n"/>
+      <c r="V7" s="32" t="n"/>
+      <c r="W7" s="32" t="n"/>
+      <c r="X7" s="32" t="n"/>
+      <c r="Y7" s="32" t="n"/>
+      <c r="Z7" s="32" t="n"/>
+      <c r="AA7" s="32" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="33" t="n"/>
@@ -5046,11 +2235,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="N4:O4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:AA15">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>AND(N($B8)&gt;0,N($C8)&gt;=N($B8),$B8&lt;=D$7,$C8&gt;=D$6)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -6496,10 +3680,7 @@
       <c r="D7" s="48" t="n"/>
       <c r="E7" s="49" t="n"/>
       <c r="F7" s="6" t="n"/>
-      <c r="G7" s="50">
-        <f>IF(OR(N(D7)=0,N(E7)=0),"",D7*E7)</f>
-        <v/>
-      </c>
+      <c r="G7" s="50" t="n"/>
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="24" t="inlineStr">
         <is>
@@ -6525,10 +3706,7 @@
       <c r="D8" s="48" t="n"/>
       <c r="E8" s="49" t="n"/>
       <c r="F8" s="6" t="n"/>
-      <c r="G8" s="50">
-        <f>IF(OR(N(D8)=0,N(E8)=0),"",D8*E8)</f>
-        <v/>
-      </c>
+      <c r="G8" s="50" t="n"/>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="24" t="inlineStr">
         <is>
@@ -6554,10 +3732,7 @@
       <c r="D9" s="48" t="n"/>
       <c r="E9" s="49" t="n"/>
       <c r="F9" s="6" t="n"/>
-      <c r="G9" s="50">
-        <f>IF(OR(N(D9)=0,N(E9)=0),"",D9*E9)</f>
-        <v/>
-      </c>
+      <c r="G9" s="50" t="n"/>
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="24" t="inlineStr">
         <is>
@@ -6583,10 +3758,7 @@
       <c r="D10" s="48" t="n"/>
       <c r="E10" s="49" t="n"/>
       <c r="F10" s="6" t="n"/>
-      <c r="G10" s="50">
-        <f>IF(OR(N(D10)=0,N(E10)=0),"",D10*E10)</f>
-        <v/>
-      </c>
+      <c r="G10" s="50" t="n"/>
       <c r="H10" s="6" t="n"/>
       <c r="I10" s="24" t="inlineStr">
         <is>
@@ -6604,10 +3776,7 @@
       <c r="D11" s="48" t="n"/>
       <c r="E11" s="49" t="n"/>
       <c r="F11" s="6" t="n"/>
-      <c r="G11" s="50">
-        <f>IF(OR(N(D11)=0,N(E11)=0),"",D11*E11)</f>
-        <v/>
-      </c>
+      <c r="G11" s="50" t="n"/>
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="24" t="n"/>
       <c r="J11" s="6" t="n"/>
@@ -6621,10 +3790,7 @@
       <c r="D12" s="48" t="n"/>
       <c r="E12" s="49" t="n"/>
       <c r="F12" s="6" t="n"/>
-      <c r="G12" s="50">
-        <f>IF(OR(N(D12)=0,N(E12)=0),"",D12*E12)</f>
-        <v/>
-      </c>
+      <c r="G12" s="50" t="n"/>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="24" t="n"/>
       <c r="J12" s="6" t="n"/>
@@ -6642,10 +3808,7 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="6" t="n"/>
       <c r="F13" s="6" t="n"/>
-      <c r="G13" s="51">
-        <f>IF(SUM(G7:G12)=0,"",SUM(G7:G12))</f>
-        <v/>
-      </c>
+      <c r="G13" s="51" t="n"/>
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="25" t="inlineStr"/>
       <c r="J13" s="6" t="n"/>
@@ -6723,10 +3886,7 @@
       <c r="F17" s="48" t="n"/>
       <c r="G17" s="49" t="n"/>
       <c r="H17" s="6" t="n"/>
-      <c r="I17" s="52">
-        <f>IF(OR(N(F17)=0,N(G17)=0),"",F17*G17)</f>
-        <v/>
-      </c>
+      <c r="I17" s="52" t="n"/>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="24" t="n"/>
       <c r="L17" s="6" t="n"/>
@@ -6752,10 +3912,7 @@
       <c r="F18" s="48" t="n"/>
       <c r="G18" s="49" t="n"/>
       <c r="H18" s="6" t="n"/>
-      <c r="I18" s="52">
-        <f>IF(OR(N(F18)=0,N(G18)=0),"",F18*G18)</f>
-        <v/>
-      </c>
+      <c r="I18" s="52" t="n"/>
       <c r="J18" s="6" t="n"/>
       <c r="K18" s="24" t="n"/>
       <c r="L18" s="6" t="n"/>
@@ -6781,10 +3938,7 @@
       <c r="F19" s="48" t="n"/>
       <c r="G19" s="49" t="n"/>
       <c r="H19" s="6" t="n"/>
-      <c r="I19" s="52">
-        <f>IF(OR(N(F19)=0,N(G19)=0),"",F19*G19)</f>
-        <v/>
-      </c>
+      <c r="I19" s="52" t="n"/>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="24" t="n"/>
       <c r="L19" s="6" t="n"/>
@@ -6810,10 +3964,7 @@
       <c r="F20" s="48" t="n"/>
       <c r="G20" s="49" t="n"/>
       <c r="H20" s="6" t="n"/>
-      <c r="I20" s="52">
-        <f>IF(OR(N(F20)=0,N(G20)=0),"",F20*G20)</f>
-        <v/>
-      </c>
+      <c r="I20" s="52" t="n"/>
       <c r="J20" s="6" t="n"/>
       <c r="K20" s="24" t="n"/>
       <c r="L20" s="6" t="n"/>
@@ -6839,10 +3990,7 @@
       <c r="F21" s="48" t="n"/>
       <c r="G21" s="49" t="n"/>
       <c r="H21" s="6" t="n"/>
-      <c r="I21" s="52">
-        <f>IF(OR(N(F21)=0,N(G21)=0),"",F21*G21)</f>
-        <v/>
-      </c>
+      <c r="I21" s="52" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="24" t="n"/>
       <c r="L21" s="6" t="n"/>
@@ -6856,10 +4004,7 @@
       <c r="F22" s="48" t="n"/>
       <c r="G22" s="49" t="n"/>
       <c r="H22" s="6" t="n"/>
-      <c r="I22" s="52">
-        <f>IF(OR(N(F22)=0,N(G22)=0),"",F22*G22)</f>
-        <v/>
-      </c>
+      <c r="I22" s="52" t="n"/>
       <c r="J22" s="6" t="n"/>
       <c r="K22" s="24" t="n"/>
       <c r="L22" s="6" t="n"/>
@@ -6877,10 +4022,7 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="6" t="n"/>
       <c r="H23" s="6" t="n"/>
-      <c r="I23" s="53">
-        <f>IF(SUM(I17:I22)=0,"",SUM(I17:I22))</f>
-        <v/>
-      </c>
+      <c r="I23" s="53" t="n"/>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="25" t="inlineStr"/>
       <c r="L23" s="6" t="n"/>

--- a/web/public/forms/otak-sigong.xlsx
+++ b/web/public/forms/otak-sigong.xlsx
@@ -815,7 +815,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -4161,7 +4161,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
